--- a/docs/modelos_importacao/02_Exemplo_Membros_TESTE.xlsx
+++ b/docs/modelos_importacao/02_Exemplo_Membros_TESTE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pessoas seguras'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pessoas seguras'!$A$1:$F$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leia-me'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -598,8 +599,788 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mendes</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>28897</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CONJUGE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Teresa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mendes</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>29754</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FILHO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mendes</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>39052</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ASCENDENTE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mendes</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>18378</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>33859</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FILHO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tiago</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>43503</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Domingos</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>25049</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONJUGE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Luísa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Domingos</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>25846</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-012</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FILHO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Domingos</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>36179</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-013</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Helena</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>34780</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>31761</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-015</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CONJUGE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>32536</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-016</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FILHO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Beatriz</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>42874</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-017</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FILHO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>44442</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lopes</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>27436</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OUTRO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Clara</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lopes</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>37810</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pires</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>36491</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-021</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cardoso</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>30410</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CONJUGE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cardoso</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>31280</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FILHO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cardoso</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>41192</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Domingas</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sebastião</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>33054</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FILHO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sebastião</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>42432</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ASCENDENTE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Albertina</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sebastião</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>21531</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-027</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>João</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kiala</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>26519</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-028</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CONJUGE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Esperança</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kiala</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>27804</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-029</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TITULAR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tavares</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>35435</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-030</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -610,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -637,7 +1418,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Pessoas fictícias para testar a importação.</t>
+          <t>30 pessoas fictícias de uma empresa (12 titulares com os seus dependentes).</t>
         </is>
       </c>
     </row>
@@ -661,7 +1442,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TITULAR, CONJUGE e FILHO têm de existir no catálogo do tenant.</t>
+          <t>TITULAR, CONJUGE, FILHO, ASCENDENTE e OUTRO têm de existir no catálogo do tenant.</t>
         </is>
       </c>
     </row>
@@ -674,6 +1455,18 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Use o modelo vazio e substitua pelos dados reais autorizados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tem vários titulares: importe num cliente empresa (um cliente individual só aceita um titular).</t>
         </is>
       </c>
     </row>
